--- a/artfynd/A 60566-2022 artfynd.xlsx
+++ b/artfynd/A 60566-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60566-2022 artfynd.xlsx
+++ b/artfynd/A 60566-2022 artfynd.xlsx
@@ -1033,7 +1033,7 @@
         <v>111631824</v>
       </c>
       <c r="B5" t="n">
-        <v>90220</v>
+        <v>90230</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 60566-2022 artfynd.xlsx
+++ b/artfynd/A 60566-2022 artfynd.xlsx
@@ -1033,7 +1033,7 @@
         <v>111631824</v>
       </c>
       <c r="B5" t="n">
-        <v>90230</v>
+        <v>90242</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 60566-2022 artfynd.xlsx
+++ b/artfynd/A 60566-2022 artfynd.xlsx
@@ -1033,7 +1033,7 @@
         <v>111631824</v>
       </c>
       <c r="B5" t="n">
-        <v>90242</v>
+        <v>90243</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 60566-2022 artfynd.xlsx
+++ b/artfynd/A 60566-2022 artfynd.xlsx
@@ -1033,7 +1033,7 @@
         <v>111631824</v>
       </c>
       <c r="B5" t="n">
-        <v>90243</v>
+        <v>90246</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 60566-2022 artfynd.xlsx
+++ b/artfynd/A 60566-2022 artfynd.xlsx
@@ -1033,7 +1033,7 @@
         <v>111631824</v>
       </c>
       <c r="B5" t="n">
-        <v>90246</v>
+        <v>90252</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 60566-2022 artfynd.xlsx
+++ b/artfynd/A 60566-2022 artfynd.xlsx
@@ -1033,7 +1033,7 @@
         <v>111631824</v>
       </c>
       <c r="B5" t="n">
-        <v>90252</v>
+        <v>90253</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 60566-2022 artfynd.xlsx
+++ b/artfynd/A 60566-2022 artfynd.xlsx
@@ -1033,7 +1033,7 @@
         <v>111631824</v>
       </c>
       <c r="B5" t="n">
-        <v>90253</v>
+        <v>90260</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 60566-2022 artfynd.xlsx
+++ b/artfynd/A 60566-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>106348256</v>
       </c>
       <c r="B2" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450990.6654319112</v>
+        <v>450991</v>
       </c>
       <c r="R2" t="n">
-        <v>7031678.107316895</v>
+        <v>7031678</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2023-02-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-02-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -793,15 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106355908</v>
+        <v>106347660</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,49 +789,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nilshallen Alsen, Jmt</t>
+          <t>Nilshallen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450946.4961568424</v>
+        <v>450991</v>
       </c>
       <c r="R3" t="n">
-        <v>7031694.467085585</v>
+        <v>7031678</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,19 +847,9 @@
           <t>2023-02-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-02-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,27 +864,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Johan Råghall, Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106347660</v>
+        <v>106355907</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,38 +887,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nilshallen, Jmt</t>
+          <t>Nilshallen Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450990.6654319112</v>
+        <v>450698</v>
       </c>
       <c r="R4" t="n">
-        <v>7031678.107316895</v>
+        <v>7031764</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,26 +952,16 @@
           <t>2023-02-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-02-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1018,68 +969,72 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Råghall, Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111631824</v>
+        <v>106355908</v>
       </c>
       <c r="B5" t="n">
-        <v>90260</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>233196</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällfotad fingersvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria rufescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Corner</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nilshallen, Nilshallen, Jmt</t>
+          <t>Nilshallen Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450824</v>
+        <v>450947</v>
       </c>
       <c r="R5" t="n">
-        <v>7031623</v>
+        <v>7031694</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,17 +1058,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
+          <t>2023-02-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På tidigare öppen hagmark som nu har växt igen med gran. Cirka 60-80 åriga granar med förekomster av gamla jättetallar. Äldre granskog ligger i anslutning.</t>
+          <t>2023-02-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,22 +1072,233 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>111631824</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91433</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>233196</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fjällfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ramaria rufescens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Corner</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nilshallen, Nilshallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>450824</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7031623</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På tidigare öppen hagmark som nu har växt igen med gran. Cirka 60-80 åriga granar med förekomster av gamla jättetallar. Äldre granskog ligger i anslutning.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Rashid Kadhim</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Rashid Kadhim</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128337962</v>
+      </c>
+      <c r="B7" t="n">
+        <v>89104</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>805</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Scharlakansvaxing</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hygrocybe punicea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nilshallen, Nilshallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>450935</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7031799</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Bryn mellan hygge och äldre granskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60566-2022 artfynd.xlsx
+++ b/artfynd/A 60566-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1090,51 +1090,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111631824</v>
+        <v>134626003</v>
       </c>
       <c r="B6" t="n">
-        <v>91433</v>
+        <v>99533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>233196</v>
+        <v>219880</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällfotad fingersvamp</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria rufescens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Corner</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nilshallen, Nilshallen, Jmt</t>
+          <t>Nilshallen, Viken 3:1, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450824</v>
+        <v>451044</v>
       </c>
       <c r="R6" t="n">
-        <v>7031623</v>
+        <v>7031701</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,17 +1159,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På tidigare öppen hagmark som nu har växt igen med gran. Cirka 60-80 åriga granar med förekomster av gamla jättetallar. Äldre granskog ligger i anslutning.</t>
+          <t>Ca 50-75 m upp i skogen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1184,44 +1185,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Göran Dahl</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Göran Dahl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128337962</v>
+        <v>111631824</v>
       </c>
       <c r="B7" t="n">
-        <v>89104</v>
+        <v>91433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>805</v>
+        <v>233196</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Scharlakansvaxing</t>
+          <t>Fjällfotad fingersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Ramaria rufescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
+          <t>(Schaeff.) Corner</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,13 +1235,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>450935</v>
+        <v>450824</v>
       </c>
       <c r="R7" t="n">
-        <v>7031799</v>
+        <v>7031623</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1264,12 +1265,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På tidigare öppen hagmark som nu har växt igen med gran. Cirka 60-80 åriga granar med förekomster av gamla jättetallar. Äldre granskog ligger i anslutning.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,11 +1288,6 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Bryn mellan hygge och äldre granskog</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1299,6 +1300,112 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128337962</v>
+      </c>
+      <c r="B8" t="n">
+        <v>89104</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>805</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Scharlakansvaxing</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hygrocybe punicea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nilshallen, Nilshallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>450935</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7031799</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Bryn mellan hygge och äldre granskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60566-2022 artfynd.xlsx
+++ b/artfynd/A 60566-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128337962</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106348256</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106347660</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106355907</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106355908</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,6 +1330,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134626003</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1406,8 +1441,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111631824</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>